--- a/aulas/09set/A55_UC01_11set/public/dados/dengue_pr_limpo.xlsx
+++ b/aulas/09set/A55_UC01_11set/public/dados/dengue_pr_limpo.xlsx
@@ -5525,7 +5525,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5555,7 +5555,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5645,7 +5645,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5765,7 +5765,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5795,7 +5795,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5825,7 +5825,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5855,7 +5855,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5885,7 +5885,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5915,7 +5915,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5945,7 +5945,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6125,7 +6125,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6185,7 +6185,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6215,7 +6215,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Jacarezinho</t>
+          <t>Joaquim Távora</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
